--- a/grupos/3BLCM - Estadisticos 20231.xlsx
+++ b/grupos/3BLCM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="93">
   <si>
     <t>Materia</t>
   </si>
@@ -98,6 +98,9 @@
     <t>HERNANDEZ VASQUEZ ALEXIS</t>
   </si>
   <si>
+    <t>LOPEZ CIRUELO LUISA MARIA</t>
+  </si>
+  <si>
     <t>MALDONADO RAMON JOSE ALBIN</t>
   </si>
   <si>
@@ -212,10 +215,10 @@
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
     <t>NC</t>
@@ -655,7 +658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y40"/>
+  <dimension ref="A1:Y41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -801,10 +804,10 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>-1</v>
@@ -813,10 +816,10 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -849,7 +852,7 @@
         <v>7</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -878,10 +881,10 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -890,10 +893,10 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -914,7 +917,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -926,10 +929,10 @@
         <v>10</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -955,10 +958,10 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -967,10 +970,10 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1003,10 +1006,10 @@
         <v>8</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1032,10 +1035,10 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -1044,10 +1047,10 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1109,10 +1112,10 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1121,10 +1124,10 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1157,7 +1160,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1186,10 +1189,10 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -1198,10 +1201,10 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1263,10 +1266,10 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>-1</v>
@@ -1275,10 +1278,10 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1299,7 +1302,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>6</v>
@@ -1340,10 +1343,10 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
         <v>-1</v>
@@ -1352,10 +1355,10 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1388,7 +1391,7 @@
         <v>7</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1417,10 +1420,10 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -1429,10 +1432,10 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1453,7 +1456,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>8</v>
@@ -1465,10 +1468,10 @@
         <v>7</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1494,10 +1497,10 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -1506,10 +1509,10 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1530,7 +1533,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>6</v>
@@ -1542,10 +1545,10 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1571,10 +1574,10 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <v>-1</v>
@@ -1583,10 +1586,10 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1648,10 +1651,10 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>-1</v>
@@ -1660,10 +1663,10 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1725,10 +1728,10 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
         <v>-1</v>
@@ -1737,10 +1740,10 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1773,7 +1776,7 @@
         <v>10</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y16">
         <v>9</v>
@@ -1802,10 +1805,10 @@
         <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
         <v>-1</v>
@@ -1814,10 +1817,10 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1864,25 +1867,25 @@
         <v>8</v>
       </c>
       <c r="C18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E18">
         <v>7</v>
       </c>
       <c r="F18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
         <v>-1</v>
@@ -1891,10 +1894,10 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1918,19 +1921,19 @@
         <v>8</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>7</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1938,28 +1941,28 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -1968,10 +1971,10 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -1992,22 +1995,22 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2015,28 +2018,28 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <v>-1</v>
@@ -2045,10 +2048,10 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2069,19 +2072,19 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2092,28 +2095,28 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G21">
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
         <v>-1</v>
@@ -2122,10 +2125,10 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2146,19 +2149,19 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -2181,16 +2184,16 @@
         <v>10</v>
       </c>
       <c r="F22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G22">
         <v>10</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
         <v>-1</v>
@@ -2199,10 +2202,10 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2235,7 +2238,7 @@
         <v>10</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y22">
         <v>10</v>
@@ -2249,25 +2252,25 @@
         <v>10</v>
       </c>
       <c r="C23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E23">
         <v>10</v>
       </c>
       <c r="F23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G23">
         <v>10</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -2276,10 +2279,10 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2303,10 +2306,10 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>10</v>
@@ -2323,28 +2326,28 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
         <v>-1</v>
@@ -2353,10 +2356,10 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2377,22 +2380,22 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2403,37 +2406,37 @@
         <v>9</v>
       </c>
       <c r="C25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25">
+        <v>6</v>
+      </c>
+      <c r="E25">
+        <v>8</v>
+      </c>
+      <c r="F25">
+        <v>7</v>
+      </c>
+      <c r="G25">
+        <v>9</v>
+      </c>
+      <c r="H25">
+        <v>6</v>
+      </c>
+      <c r="I25">
+        <v>6</v>
+      </c>
+      <c r="J25">
+        <v>-1</v>
+      </c>
+      <c r="K25">
+        <v>-1</v>
+      </c>
+      <c r="L25">
         <v>5</v>
       </c>
-      <c r="E25">
-        <v>7</v>
-      </c>
-      <c r="F25">
-        <v>10</v>
-      </c>
-      <c r="G25">
-        <v>10</v>
-      </c>
-      <c r="H25">
-        <v>-1</v>
-      </c>
-      <c r="I25">
-        <v>-1</v>
-      </c>
-      <c r="J25">
-        <v>-1</v>
-      </c>
-      <c r="K25">
-        <v>-1</v>
-      </c>
-      <c r="L25">
-        <v>-1</v>
-      </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2454,22 +2457,22 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2477,28 +2480,28 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
         <v>-1</v>
@@ -2507,10 +2510,10 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2531,22 +2534,22 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V26">
         <v>5</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2557,37 +2560,37 @@
         <v>8</v>
       </c>
       <c r="C27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D27">
         <v>4</v>
       </c>
       <c r="E27">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F27">
+        <v>8</v>
+      </c>
+      <c r="G27">
+        <v>8</v>
+      </c>
+      <c r="H27">
+        <v>7</v>
+      </c>
+      <c r="I27">
+        <v>7</v>
+      </c>
+      <c r="J27">
+        <v>-1</v>
+      </c>
+      <c r="K27">
+        <v>-1</v>
+      </c>
+      <c r="L27">
         <v>5</v>
       </c>
-      <c r="G27">
-        <v>8</v>
-      </c>
-      <c r="H27">
-        <v>-1</v>
-      </c>
-      <c r="I27">
-        <v>-1</v>
-      </c>
-      <c r="J27">
-        <v>-1</v>
-      </c>
-      <c r="K27">
-        <v>-1</v>
-      </c>
-      <c r="L27">
-        <v>-1</v>
-      </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2611,16 +2614,16 @@
         <v>8</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>5</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>8</v>
@@ -2631,28 +2634,28 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D28">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F28">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <v>-1</v>
@@ -2661,10 +2664,10 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2685,22 +2688,22 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>7</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2708,10 +2711,10 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29">
         <v>9</v>
@@ -2726,10 +2729,10 @@
         <v>9</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
         <v>-1</v>
@@ -2738,10 +2741,10 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2765,7 +2768,7 @@
         <v>9</v>
       </c>
       <c r="U29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -2774,7 +2777,7 @@
         <v>10</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>9</v>
@@ -2791,22 +2794,22 @@
         <v>6</v>
       </c>
       <c r="D30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F30">
         <v>8</v>
       </c>
       <c r="G30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
         <v>-1</v>
@@ -2815,10 +2818,10 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2845,16 +2848,16 @@
         <v>6</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2868,22 +2871,22 @@
         <v>6</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G31">
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>-1</v>
@@ -2892,10 +2895,10 @@
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2922,13 +2925,13 @@
         <v>6</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -2939,40 +2942,40 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E32">
+        <v>10</v>
+      </c>
+      <c r="F32">
+        <v>9</v>
+      </c>
+      <c r="G32">
+        <v>10</v>
+      </c>
+      <c r="H32">
+        <v>6</v>
+      </c>
+      <c r="I32">
+        <v>6</v>
+      </c>
+      <c r="J32">
+        <v>-1</v>
+      </c>
+      <c r="K32">
+        <v>-1</v>
+      </c>
+      <c r="L32">
         <v>5</v>
       </c>
-      <c r="F32">
-        <v>8</v>
-      </c>
-      <c r="G32">
-        <v>8</v>
-      </c>
-      <c r="H32">
-        <v>-1</v>
-      </c>
-      <c r="I32">
-        <v>-1</v>
-      </c>
-      <c r="J32">
-        <v>-1</v>
-      </c>
-      <c r="K32">
-        <v>-1</v>
-      </c>
-      <c r="L32">
-        <v>-1</v>
-      </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -2993,22 +2996,22 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W32">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3016,28 +3019,28 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E33">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J33">
         <v>-1</v>
@@ -3046,10 +3049,10 @@
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3070,16 +3073,16 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X33">
         <v>7</v>
@@ -3093,28 +3096,28 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D34">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J34">
         <v>-1</v>
@@ -3123,10 +3126,10 @@
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3147,22 +3150,22 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V34">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3170,28 +3173,28 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C35">
         <v>6</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G35">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J35">
         <v>-1</v>
@@ -3200,10 +3203,10 @@
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3230,16 +3233,16 @@
         <v>6</v>
       </c>
       <c r="V35">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y35">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3247,28 +3250,28 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C36">
+        <v>6</v>
+      </c>
+      <c r="D36">
         <v>5</v>
       </c>
-      <c r="D36">
-        <v>4</v>
-      </c>
       <c r="E36">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J36">
         <v>-1</v>
@@ -3277,10 +3280,10 @@
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3301,19 +3304,19 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V36">
         <v>5</v>
       </c>
       <c r="W36">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X36">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y36">
         <v>8</v>
@@ -3324,28 +3327,28 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D37">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F37">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J37">
         <v>-1</v>
@@ -3354,10 +3357,10 @@
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3378,22 +3381,22 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V37">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X37">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y37">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3407,22 +3410,22 @@
         <v>6</v>
       </c>
       <c r="D38">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G38">
         <v>10</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J38">
         <v>-1</v>
@@ -3431,10 +3434,10 @@
         <v>-1</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3461,13 +3464,13 @@
         <v>6</v>
       </c>
       <c r="V38">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y38">
         <v>10</v>
@@ -3481,25 +3484,25 @@
         <v>10</v>
       </c>
       <c r="C39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G39">
         <v>10</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J39">
         <v>-1</v>
@@ -3508,10 +3511,10 @@
         <v>-1</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3535,16 +3538,16 @@
         <v>10</v>
       </c>
       <c r="U39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y39">
         <v>10</v>
@@ -3555,28 +3558,28 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E40">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G40">
         <v>10</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J40">
         <v>-1</v>
@@ -3585,10 +3588,10 @@
         <v>-1</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3609,21 +3612,98 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W40">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y40">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25">
+      <c r="A41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41">
+        <v>9</v>
+      </c>
+      <c r="C41">
+        <v>7</v>
+      </c>
+      <c r="D41">
+        <v>7</v>
+      </c>
+      <c r="E41">
+        <v>8</v>
+      </c>
+      <c r="F41">
+        <v>7</v>
+      </c>
+      <c r="G41">
+        <v>10</v>
+      </c>
+      <c r="H41">
+        <v>6</v>
+      </c>
+      <c r="I41">
+        <v>7</v>
+      </c>
+      <c r="J41">
+        <v>-1</v>
+      </c>
+      <c r="K41">
+        <v>-1</v>
+      </c>
+      <c r="L41">
+        <v>6</v>
+      </c>
+      <c r="M41">
+        <v>9</v>
+      </c>
+      <c r="N41">
+        <v>-1</v>
+      </c>
+      <c r="O41">
+        <v>-1</v>
+      </c>
+      <c r="P41">
+        <v>-1</v>
+      </c>
+      <c r="Q41">
+        <v>-1</v>
+      </c>
+      <c r="R41">
+        <v>-1</v>
+      </c>
+      <c r="S41">
+        <v>-1</v>
+      </c>
+      <c r="T41">
+        <v>8</v>
+      </c>
+      <c r="U41">
+        <v>7</v>
+      </c>
+      <c r="V41">
+        <v>7</v>
+      </c>
+      <c r="W41">
+        <v>8</v>
+      </c>
+      <c r="X41">
+        <v>7</v>
+      </c>
+      <c r="Y41">
         <v>10</v>
       </c>
     </row>
@@ -3640,7 +3720,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -3649,7 +3729,7 @@
     <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3657,7 +3737,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -3665,7 +3745,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -3745,7 +3825,7 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -3763,7 +3843,7 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J4">
         <v>100</v>
@@ -3781,7 +3861,7 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P4">
         <v>100</v>
@@ -3804,7 +3884,7 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -3822,7 +3902,7 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J5">
         <v>100</v>
@@ -3840,7 +3920,7 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -3863,7 +3943,7 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D6">
         <v>100</v>
@@ -3881,7 +3961,7 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -3893,13 +3973,13 @@
         <v>100</v>
       </c>
       <c r="M6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N6">
         <v>100</v>
       </c>
       <c r="O6">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -3911,7 +3991,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3922,7 +4002,7 @@
         <v>95</v>
       </c>
       <c r="C7">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D7">
         <v>100</v>
@@ -3937,10 +4017,10 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -3955,10 +4035,10 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O7">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -3981,7 +4061,7 @@
         <v>100</v>
       </c>
       <c r="C8">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D8">
         <v>100</v>
@@ -3999,7 +4079,7 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -4017,7 +4097,7 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -4040,7 +4120,7 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D9">
         <v>100</v>
@@ -4058,7 +4138,7 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -4076,7 +4156,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -4099,7 +4179,7 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D10">
         <v>100</v>
@@ -4117,7 +4197,7 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -4135,7 +4215,7 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -4158,7 +4238,7 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D11">
         <v>100</v>
@@ -4176,7 +4256,7 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J11">
         <v>100</v>
@@ -4194,7 +4274,7 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -4217,7 +4297,7 @@
         <v>100</v>
       </c>
       <c r="C12">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D12">
         <v>100</v>
@@ -4235,7 +4315,7 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -4253,7 +4333,7 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P12">
         <v>100</v>
@@ -4276,7 +4356,7 @@
         <v>100</v>
       </c>
       <c r="C13">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D13">
         <v>100</v>
@@ -4294,7 +4374,7 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J13">
         <v>100</v>
@@ -4312,7 +4392,7 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -4335,7 +4415,7 @@
         <v>100</v>
       </c>
       <c r="C14">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D14">
         <v>96</v>
@@ -4353,7 +4433,7 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J14">
         <v>96</v>
@@ -4371,7 +4451,7 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P14">
         <v>96</v>
@@ -4394,7 +4474,7 @@
         <v>100</v>
       </c>
       <c r="C15">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D15">
         <v>100</v>
@@ -4412,7 +4492,7 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -4430,7 +4510,7 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -4453,7 +4533,7 @@
         <v>100</v>
       </c>
       <c r="C16">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D16">
         <v>100</v>
@@ -4471,7 +4551,7 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J16">
         <v>100</v>
@@ -4489,7 +4569,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -4512,7 +4592,7 @@
         <v>90</v>
       </c>
       <c r="C17">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D17">
         <v>94</v>
@@ -4527,10 +4607,10 @@
         <v>95</v>
       </c>
       <c r="H17">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I17">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J17">
         <v>94</v>
@@ -4542,13 +4622,13 @@
         <v>100</v>
       </c>
       <c r="M17">
+        <v>92.5</v>
+      </c>
+      <c r="N17">
         <v>95</v>
       </c>
-      <c r="N17">
-        <v>90</v>
-      </c>
       <c r="O17">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P17">
         <v>94</v>
@@ -4560,7 +4640,7 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>95</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4583,7 +4663,7 @@
         <v>100</v>
       </c>
       <c r="G18">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H18">
         <v>100</v>
@@ -4601,7 +4681,7 @@
         <v>100</v>
       </c>
       <c r="M18">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N18">
         <v>100</v>
@@ -4619,7 +4699,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4630,7 +4710,7 @@
         <v>100</v>
       </c>
       <c r="C19">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D19">
         <v>100</v>
@@ -4648,7 +4728,7 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J19">
         <v>100</v>
@@ -4666,7 +4746,7 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -4689,7 +4769,7 @@
         <v>100</v>
       </c>
       <c r="C20">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D20">
         <v>100</v>
@@ -4707,7 +4787,7 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J20">
         <v>100</v>
@@ -4725,7 +4805,7 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -4748,7 +4828,7 @@
         <v>100</v>
       </c>
       <c r="C21">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D21">
         <v>100</v>
@@ -4766,7 +4846,7 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J21">
         <v>100</v>
@@ -4784,7 +4864,7 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -4807,7 +4887,7 @@
         <v>100</v>
       </c>
       <c r="C22">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D22">
         <v>100</v>
@@ -4825,7 +4905,7 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J22">
         <v>100</v>
@@ -4843,7 +4923,7 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -4866,7 +4946,7 @@
         <v>100</v>
       </c>
       <c r="C23">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D23">
         <v>100</v>
@@ -4884,7 +4964,7 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J23">
         <v>100</v>
@@ -4902,7 +4982,7 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P23">
         <v>100</v>
@@ -4925,13 +5005,13 @@
         <v>100</v>
       </c>
       <c r="C24">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D24">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E24">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="F24">
         <v>100</v>
@@ -4943,13 +5023,13 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J24">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="K24">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -4961,13 +5041,13 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P24">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="Q24">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -4984,13 +5064,13 @@
         <v>100</v>
       </c>
       <c r="C25">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D25">
         <v>96</v>
       </c>
       <c r="E25">
-        <v>94.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F25">
         <v>100</v>
@@ -5002,37 +5082,37 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J25">
         <v>96</v>
       </c>
       <c r="K25">
-        <v>94.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L25">
         <v>100</v>
       </c>
       <c r="M25">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N25">
         <v>100</v>
       </c>
       <c r="O25">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P25">
         <v>96</v>
       </c>
       <c r="Q25">
-        <v>94.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="R25">
         <v>100</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -5040,16 +5120,16 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C26">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D26">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E26">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="F26">
         <v>100</v>
@@ -5058,16 +5138,16 @@
         <v>100</v>
       </c>
       <c r="H26">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I26">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J26">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K26">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="L26">
         <v>100</v>
@@ -5076,16 +5156,16 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="O26">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P26">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q26">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="R26">
         <v>100</v>
@@ -5102,55 +5182,55 @@
         <v>90</v>
       </c>
       <c r="C27">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D27">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E27">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="F27">
         <v>100</v>
       </c>
       <c r="G27">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H27">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I27">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J27">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="K27">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="L27">
         <v>100</v>
       </c>
       <c r="M27">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="N27">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O27">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P27">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="Q27">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="R27">
         <v>100</v>
       </c>
       <c r="S27">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5158,58 +5238,58 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C28">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D28">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E28">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="F28">
         <v>100</v>
       </c>
       <c r="G28">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H28">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I28">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J28">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K28">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="L28">
         <v>100</v>
       </c>
       <c r="M28">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N28">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O28">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P28">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="Q28">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="R28">
         <v>100</v>
       </c>
       <c r="S28">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -5220,7 +5300,7 @@
         <v>100</v>
       </c>
       <c r="C29">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D29">
         <v>100</v>
@@ -5238,7 +5318,7 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J29">
         <v>100</v>
@@ -5256,7 +5336,7 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P29">
         <v>100</v>
@@ -5279,13 +5359,13 @@
         <v>100</v>
       </c>
       <c r="C30">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D30">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E30">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="F30">
         <v>100</v>
@@ -5297,13 +5377,13 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J30">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="K30">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="L30">
         <v>100</v>
@@ -5315,13 +5395,13 @@
         <v>100</v>
       </c>
       <c r="O30">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P30">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="Q30">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="R30">
         <v>100</v>
@@ -5338,55 +5418,55 @@
         <v>100</v>
       </c>
       <c r="C31">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D31">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E31">
-        <v>94.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F31">
         <v>100</v>
       </c>
       <c r="G31">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H31">
         <v>100</v>
       </c>
       <c r="I31">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J31">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K31">
-        <v>94.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L31">
         <v>100</v>
       </c>
       <c r="M31">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="N31">
         <v>100</v>
       </c>
       <c r="O31">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P31">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q31">
-        <v>94.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="R31">
         <v>100</v>
       </c>
       <c r="S31">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5397,55 +5477,55 @@
         <v>100</v>
       </c>
       <c r="C32">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D32">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E32">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="F32">
         <v>100</v>
       </c>
       <c r="G32">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H32">
         <v>100</v>
       </c>
       <c r="I32">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J32">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="K32">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="L32">
         <v>100</v>
       </c>
       <c r="M32">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="N32">
         <v>100</v>
       </c>
       <c r="O32">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P32">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="Q32">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="R32">
         <v>100</v>
       </c>
       <c r="S32">
-        <v>100</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5456,13 +5536,13 @@
         <v>100</v>
       </c>
       <c r="C33">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D33">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E33">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="F33">
         <v>100</v>
@@ -5474,13 +5554,13 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J33">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="K33">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="L33">
         <v>100</v>
@@ -5492,13 +5572,13 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P33">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="Q33">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="R33">
         <v>100</v>
@@ -5515,13 +5595,13 @@
         <v>100</v>
       </c>
       <c r="C34">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D34">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E34">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="F34">
         <v>100</v>
@@ -5533,13 +5613,13 @@
         <v>100</v>
       </c>
       <c r="I34">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J34">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K34">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="L34">
         <v>100</v>
@@ -5551,13 +5631,13 @@
         <v>100</v>
       </c>
       <c r="O34">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P34">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q34">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="R34">
         <v>100</v>
@@ -5574,13 +5654,13 @@
         <v>100</v>
       </c>
       <c r="C35">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D35">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E35">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="F35">
         <v>100</v>
@@ -5592,37 +5672,37 @@
         <v>100</v>
       </c>
       <c r="I35">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J35">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="K35">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="L35">
         <v>100</v>
       </c>
       <c r="M35">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N35">
         <v>100</v>
       </c>
       <c r="O35">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P35">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="Q35">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="R35">
         <v>100</v>
       </c>
       <c r="S35">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5630,16 +5710,16 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C36">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D36">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E36">
-        <v>100</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F36">
         <v>100</v>
@@ -5648,16 +5728,16 @@
         <v>100</v>
       </c>
       <c r="H36">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I36">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J36">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K36">
-        <v>100</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L36">
         <v>100</v>
@@ -5666,16 +5746,16 @@
         <v>100</v>
       </c>
       <c r="N36">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O36">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P36">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="Q36">
-        <v>100</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="R36">
         <v>100</v>
@@ -5689,10 +5769,10 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C37">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D37">
         <v>100</v>
@@ -5707,10 +5787,10 @@
         <v>100</v>
       </c>
       <c r="H37">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I37">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J37">
         <v>100</v>
@@ -5725,10 +5805,10 @@
         <v>100</v>
       </c>
       <c r="N37">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O37">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P37">
         <v>100</v>
@@ -5751,7 +5831,7 @@
         <v>100</v>
       </c>
       <c r="C38">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D38">
         <v>100</v>
@@ -5769,7 +5849,7 @@
         <v>100</v>
       </c>
       <c r="I38">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J38">
         <v>100</v>
@@ -5787,7 +5867,7 @@
         <v>100</v>
       </c>
       <c r="O38">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P38">
         <v>100</v>
@@ -5810,7 +5890,7 @@
         <v>100</v>
       </c>
       <c r="C39">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D39">
         <v>100</v>
@@ -5828,7 +5908,7 @@
         <v>100</v>
       </c>
       <c r="I39">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J39">
         <v>100</v>
@@ -5846,7 +5926,7 @@
         <v>100</v>
       </c>
       <c r="O39">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P39">
         <v>100</v>
@@ -5869,54 +5949,113 @@
         <v>100</v>
       </c>
       <c r="C40">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D40">
+        <v>100</v>
+      </c>
+      <c r="E40">
+        <v>100</v>
+      </c>
+      <c r="F40">
+        <v>100</v>
+      </c>
+      <c r="G40">
+        <v>100</v>
+      </c>
+      <c r="H40">
+        <v>100</v>
+      </c>
+      <c r="I40">
+        <v>93</v>
+      </c>
+      <c r="J40">
+        <v>100</v>
+      </c>
+      <c r="K40">
+        <v>100</v>
+      </c>
+      <c r="L40">
+        <v>100</v>
+      </c>
+      <c r="M40">
+        <v>100</v>
+      </c>
+      <c r="N40">
+        <v>100</v>
+      </c>
+      <c r="O40">
+        <v>93</v>
+      </c>
+      <c r="P40">
+        <v>100</v>
+      </c>
+      <c r="Q40">
+        <v>100</v>
+      </c>
+      <c r="R40">
+        <v>100</v>
+      </c>
+      <c r="S40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19">
+      <c r="A41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41">
+        <v>100</v>
+      </c>
+      <c r="C41">
+        <v>87</v>
+      </c>
+      <c r="D41">
         <v>96</v>
       </c>
-      <c r="E40">
+      <c r="E41">
         <v>94.3</v>
       </c>
-      <c r="F40">
-        <v>100</v>
-      </c>
-      <c r="G40">
-        <v>100</v>
-      </c>
-      <c r="H40">
-        <v>100</v>
-      </c>
-      <c r="I40">
-        <v>100</v>
-      </c>
-      <c r="J40">
+      <c r="F41">
+        <v>100</v>
+      </c>
+      <c r="G41">
+        <v>100</v>
+      </c>
+      <c r="H41">
+        <v>100</v>
+      </c>
+      <c r="I41">
+        <v>93</v>
+      </c>
+      <c r="J41">
         <v>96</v>
       </c>
-      <c r="K40">
+      <c r="K41">
         <v>94.3</v>
       </c>
-      <c r="L40">
-        <v>100</v>
-      </c>
-      <c r="M40">
-        <v>100</v>
-      </c>
-      <c r="N40">
-        <v>100</v>
-      </c>
-      <c r="O40">
-        <v>100</v>
-      </c>
-      <c r="P40">
+      <c r="L41">
+        <v>100</v>
+      </c>
+      <c r="M41">
+        <v>100</v>
+      </c>
+      <c r="N41">
+        <v>100</v>
+      </c>
+      <c r="O41">
+        <v>93</v>
+      </c>
+      <c r="P41">
         <v>96</v>
       </c>
-      <c r="Q40">
+      <c r="Q41">
         <v>94.3</v>
       </c>
-      <c r="R40">
-        <v>100</v>
-      </c>
-      <c r="S40">
+      <c r="R41">
+        <v>100</v>
+      </c>
+      <c r="S41">
         <v>100</v>
       </c>
     </row>
@@ -5945,31 +6084,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -5977,22 +6116,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2">
         <v>8</v>
       </c>
       <c r="F2" s="2">
-        <v>78.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="H2">
         <v>7.1</v>
@@ -6009,25 +6148,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>91.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="G3" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="H3">
         <v>8.1</v>
-      </c>
-      <c r="H3">
-        <v>8.199999999999999</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6041,22 +6180,22 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>91.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="H4">
         <v>8.199999999999999</v>
@@ -6073,25 +6212,25 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>94.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="G5" s="2">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6102,28 +6241,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6">
         <v>37</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="H6">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6134,16 +6273,16 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -6155,7 +6294,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6180,16 +6319,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6214,22 +6353,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -6240,19 +6379,19 @@
         <v>22330051920133</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6263,19 +6402,19 @@
         <v>22330051920133</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6286,19 +6425,19 @@
         <v>22330051920352</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6309,19 +6448,19 @@
         <v>22330051920352</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6332,19 +6471,19 @@
         <v>22330051920128</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6355,19 +6494,19 @@
         <v>22330051920248</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6378,19 +6517,19 @@
         <v>22330061460548</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6401,19 +6540,19 @@
         <v>22330051920110</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6424,19 +6563,19 @@
         <v>22330051920354</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6447,19 +6586,19 @@
         <v>22330051920145</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G11">
         <v>5</v>

--- a/grupos/3BLCM - Estadisticos 20231.xlsx
+++ b/grupos/3BLCM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
   <si>
     <t>Materia</t>
   </si>
@@ -233,7 +233,10 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
   </si>
   <si>
     <t>PIÑA</t>
@@ -242,40 +245,40 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>MALDONADO</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>KARINA</t>
+    <t>ABIGAIL ANTONIA</t>
+  </si>
+  <si>
+    <t>ZURI GABRIELA</t>
   </si>
   <si>
     <t>DULCE MARIA</t>
@@ -284,19 +287,13 @@
     <t>KARENT LILIANA</t>
   </si>
   <si>
-    <t>JOSE ALBIN</t>
-  </si>
-  <si>
-    <t>NORMA ANGELICA</t>
+    <t>LUISA MARIA</t>
   </si>
   <si>
     <t>ODALIS SOFIA</t>
   </si>
   <si>
     <t>KEVIN</t>
-  </si>
-  <si>
-    <t>MELISA VIANNEY</t>
   </si>
 </sst>
 </file>
@@ -810,10 +807,10 @@
         <v>7</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -846,7 +843,7 @@
         <v>7</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>7</v>
@@ -887,10 +884,10 @@
         <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>9</v>
@@ -923,10 +920,10 @@
         <v>7</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>8</v>
@@ -964,10 +961,10 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -1000,7 +997,7 @@
         <v>6</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -1041,10 +1038,10 @@
         <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>7</v>
@@ -1077,7 +1074,7 @@
         <v>7</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -1118,10 +1115,10 @@
         <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -1154,10 +1151,10 @@
         <v>8</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -1195,10 +1192,10 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -1272,10 +1269,10 @@
         <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>7</v>
@@ -1349,10 +1346,10 @@
         <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>5</v>
@@ -1426,10 +1423,10 @@
         <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L12">
         <v>7</v>
@@ -1462,10 +1459,10 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -1503,10 +1500,10 @@
         <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
         <v>8</v>
@@ -1580,10 +1577,10 @@
         <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>7</v>
@@ -1616,10 +1613,10 @@
         <v>8</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -1657,10 +1654,10 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
         <v>10</v>
@@ -1734,10 +1731,10 @@
         <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
         <v>10</v>
@@ -1770,7 +1767,7 @@
         <v>9</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1811,10 +1808,10 @@
         <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>6</v>
@@ -1847,7 +1844,7 @@
         <v>5</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W17">
         <v>5</v>
@@ -1888,10 +1885,10 @@
         <v>7</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="L18">
         <v>7</v>
@@ -1924,10 +1921,10 @@
         <v>7</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -1965,10 +1962,10 @@
         <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>9</v>
@@ -2001,7 +1998,7 @@
         <v>9</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>7</v>
@@ -2042,10 +2039,10 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
         <v>10</v>
@@ -2119,10 +2116,10 @@
         <v>8</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
         <v>7</v>
@@ -2155,10 +2152,10 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2196,10 +2193,10 @@
         <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -2273,10 +2270,10 @@
         <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -2350,10 +2347,10 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
         <v>8</v>
@@ -2386,7 +2383,7 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -2427,10 +2424,10 @@
         <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="L25">
         <v>5</v>
@@ -2463,10 +2460,10 @@
         <v>7</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X25">
         <v>6</v>
@@ -2581,10 +2578,10 @@
         <v>7</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>5</v>
@@ -2617,7 +2614,7 @@
         <v>7</v>
       </c>
       <c r="V27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W27">
         <v>6</v>
@@ -2658,10 +2655,10 @@
         <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
         <v>5</v>
@@ -2697,7 +2694,7 @@
         <v>5</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>5</v>
@@ -2735,10 +2732,10 @@
         <v>7</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
         <v>10</v>
@@ -2774,7 +2771,7 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -2812,10 +2809,10 @@
         <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -2851,7 +2848,7 @@
         <v>9</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>9</v>
@@ -2889,10 +2886,10 @@
         <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
         <v>5</v>
@@ -2925,10 +2922,10 @@
         <v>6</v>
       </c>
       <c r="V31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>7</v>
@@ -2966,10 +2963,10 @@
         <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L32">
         <v>5</v>
@@ -3002,10 +2999,10 @@
         <v>6</v>
       </c>
       <c r="V32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>7</v>
@@ -3043,10 +3040,10 @@
         <v>7</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L33">
         <v>5</v>
@@ -3120,10 +3117,10 @@
         <v>8</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
         <v>10</v>
@@ -3197,10 +3194,10 @@
         <v>6</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L35">
         <v>9</v>
@@ -3233,7 +3230,7 @@
         <v>6</v>
       </c>
       <c r="V35">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W35">
         <v>8</v>
@@ -3274,10 +3271,10 @@
         <v>6</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L36">
         <v>6</v>
@@ -3310,10 +3307,10 @@
         <v>6</v>
       </c>
       <c r="V36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X36">
         <v>8</v>
@@ -3351,10 +3348,10 @@
         <v>6</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="L37">
         <v>5</v>
@@ -3390,7 +3387,7 @@
         <v>5</v>
       </c>
       <c r="W37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X37">
         <v>5</v>
@@ -3428,10 +3425,10 @@
         <v>6</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L38">
         <v>9</v>
@@ -3464,7 +3461,7 @@
         <v>6</v>
       </c>
       <c r="V38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W38">
         <v>8</v>
@@ -3505,10 +3502,10 @@
         <v>6</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L39">
         <v>7</v>
@@ -3544,7 +3541,7 @@
         <v>9</v>
       </c>
       <c r="W39">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X39">
         <v>8</v>
@@ -3582,10 +3579,10 @@
         <v>10</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L40">
         <v>10</v>
@@ -3659,10 +3656,10 @@
         <v>7</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L41">
         <v>6</v>
@@ -3698,7 +3695,7 @@
         <v>7</v>
       </c>
       <c r="W41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X41">
         <v>7</v>
@@ -3964,10 +3961,10 @@
         <v>93</v>
       </c>
       <c r="J6">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -3982,10 +3979,10 @@
         <v>93</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q6">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -4436,7 +4433,7 @@
         <v>93</v>
       </c>
       <c r="J14">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K14">
         <v>100</v>
@@ -4454,7 +4451,7 @@
         <v>93</v>
       </c>
       <c r="P14">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -4613,10 +4610,10 @@
         <v>93</v>
       </c>
       <c r="J17">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K17">
-        <v>91.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -4631,10 +4628,10 @@
         <v>93</v>
       </c>
       <c r="P17">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q17">
-        <v>91.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -4672,10 +4669,10 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -4690,10 +4687,10 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -4731,7 +4728,7 @@
         <v>93</v>
       </c>
       <c r="J19">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K19">
         <v>100</v>
@@ -4749,7 +4746,7 @@
         <v>93</v>
       </c>
       <c r="P19">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -5085,7 +5082,7 @@
         <v>93</v>
       </c>
       <c r="J25">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K25">
         <v>91.40000000000001</v>
@@ -5103,7 +5100,7 @@
         <v>93</v>
       </c>
       <c r="P25">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="Q25">
         <v>91.40000000000001</v>
@@ -5144,10 +5141,10 @@
         <v>93</v>
       </c>
       <c r="J26">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="K26">
-        <v>94.3</v>
+        <v>47.1</v>
       </c>
       <c r="L26">
         <v>100</v>
@@ -5162,10 +5159,10 @@
         <v>93</v>
       </c>
       <c r="P26">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="Q26">
-        <v>94.3</v>
+        <v>47.1</v>
       </c>
       <c r="R26">
         <v>100</v>
@@ -5203,10 +5200,10 @@
         <v>93</v>
       </c>
       <c r="J27">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -5221,10 +5218,10 @@
         <v>93</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -5262,7 +5259,7 @@
         <v>93</v>
       </c>
       <c r="J28">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K28">
         <v>85.7</v>
@@ -5280,7 +5277,7 @@
         <v>93</v>
       </c>
       <c r="P28">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q28">
         <v>85.7</v>
@@ -5442,7 +5439,7 @@
         <v>96</v>
       </c>
       <c r="K31">
-        <v>91.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -5460,7 +5457,7 @@
         <v>96</v>
       </c>
       <c r="Q31">
-        <v>91.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R31">
         <v>100</v>
@@ -5498,10 +5495,10 @@
         <v>93</v>
       </c>
       <c r="J32">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K32">
-        <v>94.3</v>
+        <v>90</v>
       </c>
       <c r="L32">
         <v>100</v>
@@ -5516,10 +5513,10 @@
         <v>93</v>
       </c>
       <c r="P32">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q32">
-        <v>94.3</v>
+        <v>90</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -5616,7 +5613,7 @@
         <v>93</v>
       </c>
       <c r="J34">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K34">
         <v>94.3</v>
@@ -5634,7 +5631,7 @@
         <v>93</v>
       </c>
       <c r="P34">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q34">
         <v>94.3</v>
@@ -5675,10 +5672,10 @@
         <v>93</v>
       </c>
       <c r="J35">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K35">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="L35">
         <v>100</v>
@@ -5693,10 +5690,10 @@
         <v>93</v>
       </c>
       <c r="P35">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q35">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="R35">
         <v>100</v>
@@ -5737,7 +5734,7 @@
         <v>92</v>
       </c>
       <c r="K36">
-        <v>91.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L36">
         <v>100</v>
@@ -5755,7 +5752,7 @@
         <v>92</v>
       </c>
       <c r="Q36">
-        <v>91.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R36">
         <v>100</v>
@@ -5793,10 +5790,10 @@
         <v>93</v>
       </c>
       <c r="J37">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K37">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="L37">
         <v>100</v>
@@ -5811,10 +5808,10 @@
         <v>93</v>
       </c>
       <c r="P37">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q37">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="R37">
         <v>100</v>
@@ -5914,7 +5911,7 @@
         <v>100</v>
       </c>
       <c r="K39">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="L39">
         <v>100</v>
@@ -5932,7 +5929,7 @@
         <v>100</v>
       </c>
       <c r="Q39">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="R39">
         <v>100</v>
@@ -6029,7 +6026,7 @@
         <v>93</v>
       </c>
       <c r="J41">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K41">
         <v>94.3</v>
@@ -6047,7 +6044,7 @@
         <v>93</v>
       </c>
       <c r="P41">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="Q41">
         <v>94.3</v>
@@ -6122,19 +6119,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>78.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>21.1</v>
+        <v>18.4</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6145,28 +6142,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C3">
         <v>38</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2">
-        <v>92.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="G3" s="2">
-        <v>7.9</v>
+        <v>15.8</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6177,10 +6174,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4">
         <v>38</v>
@@ -6198,7 +6195,7 @@
         <v>7.9</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6376,7 +6373,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920133</v>
+        <v>22330051920130</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
@@ -6399,7 +6396,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920133</v>
+        <v>22330051920130</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
@@ -6422,7 +6419,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920352</v>
+        <v>22330051920138</v>
       </c>
       <c r="B4" t="s">
         <v>72</v>
@@ -6445,7 +6442,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920352</v>
+        <v>22330051920138</v>
       </c>
       <c r="B5" t="s">
         <v>72</v>
@@ -6457,10 +6454,10 @@
         <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6468,7 +6465,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920128</v>
+        <v>22330051920352</v>
       </c>
       <c r="B6" t="s">
         <v>73</v>
@@ -6491,22 +6488,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920248</v>
+        <v>22330051920352</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6514,16 +6511,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330061460548</v>
+        <v>22330051920128</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -6537,19 +6534,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920110</v>
+        <v>22330051920246</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
         <v>62</v>
@@ -6560,19 +6557,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920354</v>
+        <v>22330051920110</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
         <v>62</v>
@@ -6583,19 +6580,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920145</v>
+        <v>22330051920354</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
         <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
         <v>62</v>

--- a/grupos/3BLCM - Estadisticos 20231.xlsx
+++ b/grupos/3BLCM - Estadisticos 20231.xlsx
@@ -2501,10 +2501,10 @@
         <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L26">
         <v>10</v>
@@ -2540,7 +2540,7 @@
         <v>5</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -5141,10 +5141,10 @@
         <v>93</v>
       </c>
       <c r="J26">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="K26">
-        <v>47.1</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="L26">
         <v>100</v>
@@ -5159,10 +5159,10 @@
         <v>93</v>
       </c>
       <c r="P26">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="Q26">
-        <v>47.1</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="R26">
         <v>100</v>

--- a/grupos/3BLCM - Estadisticos 20231.xlsx
+++ b/grupos/3BLCM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="80">
   <si>
     <t>Materia</t>
   </si>
@@ -206,18 +206,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
     <t>Castro Vasquez Julieta</t>
   </si>
   <si>
@@ -236,64 +236,28 @@
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
     <t>PIÑA</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
+    <t>TORRES</t>
   </si>
   <si>
     <t>OJEDA</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
+    <t>MEZA</t>
   </si>
   <si>
     <t>ABIGAIL ANTONIA</t>
   </si>
   <si>
-    <t>ZURI GABRIELA</t>
-  </si>
-  <si>
     <t>DULCE MARIA</t>
   </si>
   <si>
-    <t>KARENT LILIANA</t>
-  </si>
-  <si>
-    <t>LUISA MARIA</t>
-  </si>
-  <si>
-    <t>ODALIS SOFIA</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
+    <t>ACSA FERNANDA</t>
   </si>
 </sst>
 </file>
@@ -819,25 +783,25 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>7</v>
@@ -846,7 +810,7 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -896,25 +860,25 @@
         <v>7</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -926,7 +890,7 @@
         <v>9</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>8</v>
@@ -973,25 +937,25 @@
         <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>6</v>
@@ -1003,10 +967,10 @@
         <v>8</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1050,25 +1014,25 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>7</v>
@@ -1127,22 +1091,22 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1160,7 +1124,7 @@
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1204,22 +1168,22 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1281,22 +1245,22 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1305,7 +1269,7 @@
         <v>6</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1358,25 +1322,25 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>6</v>
@@ -1388,10 +1352,10 @@
         <v>7</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1435,37 +1399,37 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>5</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -1512,22 +1476,22 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>7</v>
@@ -1589,22 +1553,22 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1613,10 +1577,10 @@
         <v>8</v>
       </c>
       <c r="V14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -1666,22 +1630,22 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1743,25 +1707,25 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
         <v>9</v>
@@ -1820,40 +1784,40 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U17">
         <v>5</v>
       </c>
       <c r="V17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>5</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1897,22 +1861,22 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>8</v>
@@ -1921,13 +1885,13 @@
         <v>7</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>9</v>
@@ -1974,22 +1938,22 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>8</v>
@@ -1998,13 +1962,13 @@
         <v>9</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2051,25 +2015,25 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>10</v>
@@ -2128,22 +2092,22 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -2158,10 +2122,10 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2205,22 +2169,22 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2282,22 +2246,22 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>10</v>
@@ -2353,31 +2317,31 @@
         <v>9</v>
       </c>
       <c r="L24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M24">
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>10</v>
@@ -2386,10 +2350,10 @@
         <v>9</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2436,40 +2400,40 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2513,31 +2477,31 @@
         <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>6</v>
       </c>
       <c r="V26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W26">
         <v>6</v>
@@ -2546,7 +2510,7 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2590,37 +2554,37 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <v>7</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>8</v>
@@ -2667,25 +2631,25 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U28">
         <v>7</v>
@@ -2697,7 +2661,7 @@
         <v>7</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -2744,25 +2708,25 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>7</v>
@@ -2774,7 +2738,7 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>9</v>
@@ -2821,22 +2785,22 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>9</v>
@@ -2851,7 +2815,7 @@
         <v>9</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y30">
         <v>9</v>
@@ -2898,25 +2862,25 @@
         <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U31">
         <v>6</v>
@@ -2925,10 +2889,10 @@
         <v>8</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -2975,25 +2939,25 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U32">
         <v>6</v>
@@ -3002,10 +2966,10 @@
         <v>7</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>9</v>
@@ -3052,25 +3016,25 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>7</v>
@@ -3079,13 +3043,13 @@
         <v>7</v>
       </c>
       <c r="W33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3129,37 +3093,37 @@
         <v>9</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>9</v>
@@ -3206,25 +3170,25 @@
         <v>8</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U35">
         <v>6</v>
@@ -3283,37 +3247,37 @@
         <v>7</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U36">
         <v>6</v>
       </c>
       <c r="V36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y36">
         <v>8</v>
@@ -3360,22 +3324,22 @@
         <v>6</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T37">
         <v>5</v>
@@ -3393,7 +3357,7 @@
         <v>5</v>
       </c>
       <c r="Y37">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3437,25 +3401,25 @@
         <v>9</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U38">
         <v>6</v>
@@ -3464,7 +3428,7 @@
         <v>8</v>
       </c>
       <c r="W38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X38">
         <v>9</v>
@@ -3514,34 +3478,34 @@
         <v>9</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U39">
         <v>6</v>
       </c>
       <c r="V39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X39">
         <v>8</v>
@@ -3591,31 +3555,31 @@
         <v>10</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U40">
         <v>10</v>
       </c>
       <c r="V40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W40">
         <v>10</v>
@@ -3668,22 +3632,22 @@
         <v>9</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T41">
         <v>8</v>
@@ -3692,13 +3656,13 @@
         <v>7</v>
       </c>
       <c r="V41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y41">
         <v>10</v>
@@ -3858,7 +3822,7 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P4">
         <v>100</v>
@@ -3917,7 +3881,7 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -3976,19 +3940,19 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P6">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="Q6">
-        <v>97.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="R6">
         <v>100</v>
       </c>
       <c r="S6">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -4032,10 +3996,10 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>97.5</v>
+        <v>96.5</v>
       </c>
       <c r="O7">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -4094,7 +4058,7 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -4150,16 +4114,16 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="O9">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P9">
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -4212,13 +4176,13 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P10">
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -4271,13 +4235,13 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P11">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="Q11">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -4330,13 +4294,13 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P12">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="R12">
         <v>100</v>
@@ -4389,7 +4353,7 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -4448,13 +4412,13 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P14">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Q14">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="R14">
         <v>100</v>
@@ -4507,13 +4471,13 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P15">
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -4566,7 +4530,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -4622,22 +4586,22 @@
         <v>92.5</v>
       </c>
       <c r="N17">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O17">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P17">
-        <v>95</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="Q17">
-        <v>92.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="R17">
         <v>100</v>
       </c>
       <c r="S17">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4681,22 +4645,22 @@
         <v>97.5</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="O18">
         <v>100</v>
       </c>
       <c r="P18">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="Q18">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="R18">
         <v>100</v>
       </c>
       <c r="S18">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4743,10 +4707,10 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P19">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -4802,13 +4766,13 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P20">
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="R20">
         <v>100</v>
@@ -4861,7 +4825,7 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -4920,13 +4884,13 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P22">
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -4979,13 +4943,13 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P23">
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -5038,13 +5002,13 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P24">
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -5097,19 +5061,19 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P25">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="Q25">
-        <v>91.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R25">
         <v>100</v>
       </c>
       <c r="S25">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -5156,13 +5120,13 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P26">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="Q26">
-        <v>97.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="R26">
         <v>100</v>
@@ -5212,16 +5176,16 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O27">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P27">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="Q27">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -5271,22 +5235,22 @@
         <v>90</v>
       </c>
       <c r="N28">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O28">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P28">
-        <v>88</v>
+        <v>91.3</v>
       </c>
       <c r="Q28">
-        <v>85.7</v>
+        <v>89.3</v>
       </c>
       <c r="R28">
         <v>100</v>
       </c>
       <c r="S28">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -5333,13 +5297,13 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P29">
         <v>100</v>
       </c>
       <c r="Q29">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="R29">
         <v>100</v>
@@ -5392,13 +5356,13 @@
         <v>100</v>
       </c>
       <c r="O30">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P30">
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="R30">
         <v>100</v>
@@ -5448,16 +5412,16 @@
         <v>100</v>
       </c>
       <c r="N31">
-        <v>100</v>
+        <v>96.5</v>
       </c>
       <c r="O31">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P31">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="Q31">
-        <v>92.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="R31">
         <v>100</v>
@@ -5510,19 +5474,19 @@
         <v>100</v>
       </c>
       <c r="O32">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P32">
-        <v>93</v>
+        <v>93.8</v>
       </c>
       <c r="Q32">
-        <v>90</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="R32">
         <v>100</v>
       </c>
       <c r="S32">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5566,10 +5530,10 @@
         <v>100</v>
       </c>
       <c r="N33">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="O33">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -5628,13 +5592,13 @@
         <v>100</v>
       </c>
       <c r="O34">
-        <v>93</v>
+        <v>87.3</v>
       </c>
       <c r="P34">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q34">
-        <v>94.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R34">
         <v>100</v>
@@ -5684,22 +5648,22 @@
         <v>97.5</v>
       </c>
       <c r="N35">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="O35">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P35">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Q35">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="R35">
         <v>100</v>
       </c>
       <c r="S35">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5746,13 +5710,13 @@
         <v>100</v>
       </c>
       <c r="O36">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P36">
-        <v>92</v>
+        <v>93.8</v>
       </c>
       <c r="Q36">
-        <v>92.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="R36">
         <v>100</v>
@@ -5802,16 +5766,16 @@
         <v>100</v>
       </c>
       <c r="N37">
-        <v>97.5</v>
+        <v>93</v>
       </c>
       <c r="O37">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P37">
-        <v>98</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q37">
-        <v>95.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R37">
         <v>100</v>
@@ -5864,7 +5828,7 @@
         <v>100</v>
       </c>
       <c r="O38">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P38">
         <v>100</v>
@@ -5920,16 +5884,16 @@
         <v>100</v>
       </c>
       <c r="N39">
-        <v>100</v>
+        <v>96.5</v>
       </c>
       <c r="O39">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P39">
         <v>100</v>
       </c>
       <c r="Q39">
-        <v>97.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="R39">
         <v>100</v>
@@ -5982,13 +5946,13 @@
         <v>100</v>
       </c>
       <c r="O40">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P40">
         <v>100</v>
       </c>
       <c r="Q40">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="R40">
         <v>100</v>
@@ -6041,13 +6005,13 @@
         <v>100</v>
       </c>
       <c r="O41">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="P41">
-        <v>92</v>
+        <v>93.8</v>
       </c>
       <c r="Q41">
-        <v>94.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R41">
         <v>100</v>
@@ -6110,7 +6074,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
@@ -6119,19 +6083,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2">
-        <v>81.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>18.4</v>
+        <v>7.9</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6145,22 +6109,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3">
         <v>38</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>84.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>15.8</v>
+        <v>7.9</v>
       </c>
       <c r="H3">
         <v>7.8</v>
@@ -6174,28 +6138,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4">
         <v>38</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>92.09999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="G4" s="2">
-        <v>7.9</v>
+        <v>5.3</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6206,10 +6170,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C5">
         <v>38</v>
@@ -6227,7 +6191,7 @@
         <v>5.3</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6238,7 +6202,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
@@ -6259,7 +6223,7 @@
         <v>2.6</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6291,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6341,7 +6305,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6379,16 +6343,16 @@
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6396,22 +6360,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920130</v>
+        <v>22330051920352</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" t="s">
         <v>78</v>
       </c>
-      <c r="D3" t="s">
-        <v>85</v>
-      </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6419,185 +6383,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920138</v>
+        <v>22330051920144</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" t="s">
         <v>79</v>
       </c>
-      <c r="D4" t="s">
-        <v>86</v>
-      </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>62</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920138</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920352</v>
-      </c>
-      <c r="B6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D6" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920352</v>
-      </c>
-      <c r="B7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920128</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920246</v>
-      </c>
-      <c r="B9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920110</v>
-      </c>
-      <c r="B10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" t="s">
-        <v>90</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920354</v>
-      </c>
-      <c r="B11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3BLCM - Estadisticos 20231.xlsx
+++ b/grupos/3BLCM - Estadisticos 20231.xlsx
@@ -801,22 +801,22 @@
         <v>9</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -878,22 +878,22 @@
         <v>9</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -955,22 +955,22 @@
         <v>10</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1032,22 +1032,22 @@
         <v>9</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1109,22 +1109,22 @@
         <v>9</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1263,19 +1263,19 @@
         <v>10</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -1340,22 +1340,22 @@
         <v>9</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1417,22 +1417,22 @@
         <v>8</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>5</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1494,22 +1494,22 @@
         <v>9</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1571,19 +1571,19 @@
         <v>9</v>
       </c>
       <c r="T14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1725,13 +1725,13 @@
         <v>10</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1740,7 +1740,7 @@
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1808,16 +1808,16 @@
         <v>5</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>5</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1879,22 +1879,22 @@
         <v>10</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y18">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1956,22 +1956,22 @@
         <v>8</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2033,7 +2033,7 @@
         <v>10</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U20">
         <v>10</v>
@@ -2110,22 +2110,22 @@
         <v>9</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2190,7 +2190,7 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V22">
         <v>10</v>
@@ -2267,7 +2267,7 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V23">
         <v>10</v>
@@ -2341,16 +2341,16 @@
         <v>10</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U24">
         <v>10</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -2418,22 +2418,22 @@
         <v>8</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2495,22 +2495,22 @@
         <v>8</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X26">
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2572,22 +2572,22 @@
         <v>8</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2649,22 +2649,22 @@
         <v>8</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>5</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2726,22 +2726,22 @@
         <v>10</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2803,22 +2803,22 @@
         <v>10</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2880,19 +2880,19 @@
         <v>10</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -2957,22 +2957,22 @@
         <v>8</v>
       </c>
       <c r="T32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3034,22 +3034,22 @@
         <v>8</v>
       </c>
       <c r="T33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3111,22 +3111,22 @@
         <v>9</v>
       </c>
       <c r="T34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3191,19 +3191,19 @@
         <v>5</v>
       </c>
       <c r="U35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3265,22 +3265,22 @@
         <v>7</v>
       </c>
       <c r="T36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y36">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3357,7 +3357,7 @@
         <v>5</v>
       </c>
       <c r="Y37">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3419,19 +3419,19 @@
         <v>10</v>
       </c>
       <c r="T38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V38">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y38">
         <v>10</v>
@@ -3496,19 +3496,19 @@
         <v>10</v>
       </c>
       <c r="T39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y39">
         <v>10</v>
@@ -3573,13 +3573,13 @@
         <v>10</v>
       </c>
       <c r="T40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U40">
         <v>10</v>
       </c>
       <c r="V40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W40">
         <v>10</v>
@@ -3650,19 +3650,19 @@
         <v>10</v>
       </c>
       <c r="T41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U41">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y41">
         <v>10</v>
@@ -6095,7 +6095,7 @@
         <v>7.9</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6127,7 +6127,7 @@
         <v>7.9</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6159,7 +6159,7 @@
         <v>5.3</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6191,7 +6191,7 @@
         <v>5.3</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6223,7 +6223,7 @@
         <v>2.6</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>9.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/3BLCM - Estadisticos 20231.xlsx
+++ b/grupos/3BLCM - Estadisticos 20231.xlsx
@@ -801,22 +801,22 @@
         <v>9</v>
       </c>
       <c r="T4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -878,22 +878,22 @@
         <v>9</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -955,22 +955,22 @@
         <v>10</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1032,22 +1032,22 @@
         <v>9</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1109,22 +1109,22 @@
         <v>9</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1263,19 +1263,19 @@
         <v>10</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -1340,22 +1340,22 @@
         <v>9</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1417,22 +1417,22 @@
         <v>8</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>5</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1494,22 +1494,22 @@
         <v>9</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1571,19 +1571,19 @@
         <v>9</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1725,13 +1725,13 @@
         <v>10</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1740,7 +1740,7 @@
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1808,16 +1808,16 @@
         <v>5</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>5</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1879,22 +1879,22 @@
         <v>10</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1956,22 +1956,22 @@
         <v>8</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2033,7 +2033,7 @@
         <v>10</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>10</v>
@@ -2110,22 +2110,22 @@
         <v>9</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2190,7 +2190,7 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V22">
         <v>10</v>
@@ -2267,7 +2267,7 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>10</v>
@@ -2341,16 +2341,16 @@
         <v>10</v>
       </c>
       <c r="T24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>10</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -2418,22 +2418,22 @@
         <v>8</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2495,22 +2495,22 @@
         <v>8</v>
       </c>
       <c r="T26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2572,22 +2572,22 @@
         <v>8</v>
       </c>
       <c r="T27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2649,22 +2649,22 @@
         <v>8</v>
       </c>
       <c r="T28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V28">
         <v>5</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2726,22 +2726,22 @@
         <v>10</v>
       </c>
       <c r="T29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2803,22 +2803,22 @@
         <v>10</v>
       </c>
       <c r="T30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2880,19 +2880,19 @@
         <v>10</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -2957,22 +2957,22 @@
         <v>8</v>
       </c>
       <c r="T32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3034,22 +3034,22 @@
         <v>8</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3111,22 +3111,22 @@
         <v>9</v>
       </c>
       <c r="T34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y34">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3191,19 +3191,19 @@
         <v>5</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y35">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3265,22 +3265,22 @@
         <v>7</v>
       </c>
       <c r="T36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W36">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y36">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3357,7 +3357,7 @@
         <v>5</v>
       </c>
       <c r="Y37">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3419,19 +3419,19 @@
         <v>10</v>
       </c>
       <c r="T38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y38">
         <v>10</v>
@@ -3496,19 +3496,19 @@
         <v>10</v>
       </c>
       <c r="T39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y39">
         <v>10</v>
@@ -3573,13 +3573,13 @@
         <v>10</v>
       </c>
       <c r="T40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U40">
         <v>10</v>
       </c>
       <c r="V40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W40">
         <v>10</v>
@@ -3650,19 +3650,19 @@
         <v>10</v>
       </c>
       <c r="T41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U41">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y41">
         <v>10</v>
@@ -6095,7 +6095,7 @@
         <v>7.9</v>
       </c>
       <c r="H2">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6127,7 +6127,7 @@
         <v>7.9</v>
       </c>
       <c r="H3">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6159,7 +6159,7 @@
         <v>5.3</v>
       </c>
       <c r="H4">
-        <v>9.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6191,7 +6191,7 @@
         <v>5.3</v>
       </c>
       <c r="H5">
-        <v>9.699999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6223,7 +6223,7 @@
         <v>2.6</v>
       </c>
       <c r="H6">
-        <v>9.9</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>8.9</v>
       </c>
       <c r="I7">
         <v>0</v>
